--- a/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 11,6</t>
+          <t>-30,95; 8,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -2,44</t>
+          <t>-52,28; -3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 22,9</t>
+          <t>-23,01; 20,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 25,29</t>
+          <t>-32,43; 25,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 8,83</t>
+          <t>-19,77; 9,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 0,36</t>
+          <t>-36,09; 3,32</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 25,44</t>
+          <t>-45,65; 18,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,2; -3,29</t>
+          <t>-80,7; -5,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 55,93</t>
+          <t>-36,64; 47,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 55,4</t>
+          <t>-52,91; 56,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 17,83</t>
+          <t>-32,14; 20,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,44; -0,43</t>
+          <t>-59,31; 6,62</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,28; -4,21</t>
+          <t>-20,97; -4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 4,1</t>
+          <t>-20,34; 4,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,85; -4,51</t>
+          <t>-21,74; -5,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -0,85</t>
+          <t>-21,99; -1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -6,37</t>
+          <t>-17,8; -5,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,54; -2,08</t>
+          <t>-18,61; -1,89</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,36; -8,34</t>
+          <t>-38,34; -9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 8,82</t>
+          <t>-37,64; 10,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,98; -7,68</t>
+          <t>-32,93; -8,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,45; -1,57</t>
+          <t>-34,26; -2,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,06; -11,71</t>
+          <t>-29,95; -10,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; -3,8</t>
+          <t>-31,16; -2,81</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,89; -6,41</t>
+          <t>-26,17; -6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,44; -0,24</t>
+          <t>-24,98; 0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 7,06</t>
+          <t>-12,82; 7,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 3,97</t>
+          <t>-20,89; 2,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -2,09</t>
+          <t>-16,38; -2,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -1,64</t>
+          <t>-19,41; -2,09</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -12,98</t>
+          <t>-44,41; -14,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,28; -0,3</t>
+          <t>-44,19; 0,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 14,67</t>
+          <t>-21,32; 15,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 8,37</t>
+          <t>-36,71; 5,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -4,14</t>
+          <t>-28,82; -4,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,34; -3,48</t>
+          <t>-34,03; -3,87</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 4,85</t>
+          <t>-11,58; 5,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,42; -3,2</t>
+          <t>-25,1; -3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -0,55</t>
+          <t>-19,05; -0,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 1,79</t>
+          <t>-21,53; 2,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 0,28</t>
+          <t>-12,07; 0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -2,7</t>
+          <t>-19,4; -3,12</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 21,58</t>
+          <t>-36,39; 24,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,87; -13,32</t>
+          <t>-78,58; -13,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,01; -1,45</t>
+          <t>-41,22; -0,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 3,93</t>
+          <t>-46,71; 6,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 0,82</t>
+          <t>-32,43; 0,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,83; -8,75</t>
+          <t>-54,52; -10,21</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -5,42</t>
+          <t>-15,21; -5,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -10,3</t>
+          <t>-25,83; -9,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -3,08</t>
+          <t>-13,17; -3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -6,51</t>
+          <t>-18,72; -5,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -5,54</t>
+          <t>-12,62; -5,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,54; -9,67</t>
+          <t>-19,41; -9,09</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -12,81</t>
+          <t>-32,32; -12,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -23,86</t>
+          <t>-56,28; -22,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -6,07</t>
+          <t>-23,62; -6,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,79; -12,35</t>
+          <t>-33,57; -11,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -11,73</t>
+          <t>-24,67; -10,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -20,06</t>
+          <t>-39,11; -18,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 8,67</t>
+          <t>-29,97; 8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-52,28; -3,36</t>
+          <t>-52,56; -2,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 20,84</t>
+          <t>-22,0; 21,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 25,21</t>
+          <t>-28,24; 27,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 9,92</t>
+          <t>-20,1; 9,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 3,32</t>
+          <t>-36,58; 0,09</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 18,4</t>
+          <t>-45,8; 20,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,7; -5,48</t>
+          <t>-80,62; -0,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 47,38</t>
+          <t>-35,24; 53,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 56,83</t>
+          <t>-50,4; 59,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 20,21</t>
+          <t>-31,82; 19,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,31; 6,62</t>
+          <t>-60,9; 0,07</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -4,3</t>
+          <t>-21,13; -4,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 4,61</t>
+          <t>-20,29; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -5,29</t>
+          <t>-20,85; -5,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,99; -1,44</t>
+          <t>-23,04; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -5,92</t>
+          <t>-18,24; -6,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -1,89</t>
+          <t>-17,74; -1,62</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,34; -9,02</t>
+          <t>-37,85; -9,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 10,06</t>
+          <t>-38,09; 11,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,93; -8,95</t>
+          <t>-31,23; -8,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -2,5</t>
+          <t>-36,01; -1,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -10,99</t>
+          <t>-30,6; -12,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,16; -2,81</t>
+          <t>-29,69; -2,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,17; -6,98</t>
+          <t>-25,37; -6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 0,3</t>
+          <t>-25,43; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 7,69</t>
+          <t>-12,46; 6,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 2,75</t>
+          <t>-20,15; 1,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -2,09</t>
+          <t>-16,03; -2,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -2,09</t>
+          <t>-19,06; -1,46</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -14,58</t>
+          <t>-42,94; -12,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 0,51</t>
+          <t>-45,09; 1,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 15,96</t>
+          <t>-21,14; 13,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 5,73</t>
+          <t>-35,0; 4,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,82; -4,14</t>
+          <t>-28,42; -4,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -3,87</t>
+          <t>-34,57; -3,01</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 5,66</t>
+          <t>-11,35; 5,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -3,48</t>
+          <t>-23,29; -2,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -0,72</t>
+          <t>-19,24; -0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 2,16</t>
+          <t>-20,32; 1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 0,26</t>
+          <t>-12,15; 0,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,4; -3,12</t>
+          <t>-19,47; -3,47</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 24,32</t>
+          <t>-36,56; 23,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,58; -13,0</t>
+          <t>-77,56; -13,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,22; -0,99</t>
+          <t>-42,57; -1,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 6,32</t>
+          <t>-45,98; 4,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 0,75</t>
+          <t>-32,97; 1,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,52; -10,21</t>
+          <t>-54,6; -10,44</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -5,1</t>
+          <t>-15,64; -5,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -9,64</t>
+          <t>-25,94; -10,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -3,12</t>
+          <t>-12,95; -2,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -5,93</t>
+          <t>-19,57; -5,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -5,21</t>
+          <t>-12,47; -5,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -9,09</t>
+          <t>-20,57; -9,61</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -12,23</t>
+          <t>-32,68; -12,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -22,13</t>
+          <t>-56,06; -23,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -6,22</t>
+          <t>-23,08; -4,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,57; -11,34</t>
+          <t>-35,04; -10,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -10,96</t>
+          <t>-24,67; -11,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,11; -18,97</t>
+          <t>-40,7; -19,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-11,19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-29,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>-28,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,08</t>
+          <t>-16,91</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 8,85</t>
+          <t>-21,74; 22,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-52,56; -2,41</t>
+          <t>-28,47; 28,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 21,66</t>
+          <t>-31,34; 11,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 27,2</t>
+          <t>-50,19; -0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 9,49</t>
+          <t>-20,78; 8,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 0,09</t>
+          <t>-35,85; 1,54</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-19,19%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-50,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,62%</t>
+          <t>-48,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,08%</t>
+          <t>-30,01%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 20,04</t>
+          <t>-34,17; 55,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,62; -0,58</t>
+          <t>-48,25; 67,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 53,06</t>
+          <t>-47,78; 25,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 59,91</t>
+          <t>-79,61; 0,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 19,72</t>
+          <t>-33,0; 17,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 0,07</t>
+          <t>-60,06; 2,16</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-13,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-13,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-12,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-8,26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,25</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,24</t>
+          <t>-10,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,85</t>
+          <t>-11,5</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -4,28</t>
+          <t>-20,85; -4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 5,08</t>
+          <t>-23,05; -1,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,85; -5,01</t>
+          <t>-20,28; -4,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 0,24</t>
+          <t>-22,98; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,24; -6,61</t>
+          <t>-18,52; -6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -1,62</t>
+          <t>-19,58; -3,71</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-21,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-20,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-23,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-16,16%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-21,07%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-19,47%</t>
+          <t>-21,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,19%</t>
+          <t>-20,08%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,85; -9,22</t>
+          <t>-31,98; -7,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 11,3</t>
+          <t>-35,46; -2,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,23; -8,44</t>
+          <t>-36,36; -8,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,01; -1,11</t>
+          <t>-42,2; 3,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,6; -12,31</t>
+          <t>-31,06; -11,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,69; -2,38</t>
+          <t>-33,27; -6,71</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-16,16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-13,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,49</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-9,2</t>
+          <t>-15,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-11,39</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,37; -6,13</t>
+          <t>-11,76; 7,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 0,62</t>
+          <t>-19,89; 5,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 6,54</t>
+          <t>-25,89; -6,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 1,92</t>
+          <t>-27,13; -3,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -2,15</t>
+          <t>-15,64; -2,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -1,46</t>
+          <t>-20,27; -2,97</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-30,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-24,24%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-4,65%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-17,21%</t>
+          <t>-28,8%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>-21,26%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,94; -12,37</t>
+          <t>-20,14; 14,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 1,53</t>
+          <t>-34,25; 9,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 13,4</t>
+          <t>-44,32; -12,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 4,18</t>
+          <t>-46,64; -7,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,42; -4,52</t>
+          <t>-27,34; -4,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -3,01</t>
+          <t>-35,91; -5,79</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-9,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-13,53</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,28</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-9,64</t>
+          <t>-12,26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,57</t>
+          <t>-9,96</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 5,64</t>
+          <t>-18,11; -0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,29; -2,79</t>
+          <t>-20,75; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -0,56</t>
+          <t>-11,37; 4,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 1,58</t>
+          <t>-21,12; -3,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 0,53</t>
+          <t>-12,28; 0,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -3,47</t>
+          <t>-16,49; -2,17</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-22,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,87%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-9,56%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-50,07%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-22,42%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-23,28%</t>
+          <t>-45,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,69%</t>
+          <t>-29,02%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 23,41</t>
+          <t>-40,01; -1,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,56; -13,61</t>
+          <t>-44,47; 3,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,57; -1,37</t>
+          <t>-36,52; 21,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 4,75</t>
+          <t>-67,07; -11,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 1,41</t>
+          <t>-32,65; 0,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,6; -10,44</t>
+          <t>-45,54; -7,13</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-8,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-12,6</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-10,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-17,3</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-12,64</t>
+          <t>-17,07</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-14,48</t>
+          <t>-14,2</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,22</t>
+          <t>-13,25; -3,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,94; -10,11</t>
+          <t>-18,77; -6,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,37</t>
+          <t>-15,41; -5,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -5,75</t>
+          <t>-22,85; -10,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -5,26</t>
+          <t>-12,74; -5,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -9,61</t>
+          <t>-18,7; -9,74</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-15,51%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-23,47%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-22,77%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-38,41%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,51%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-23,54%</t>
+          <t>-37,89%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,27%</t>
+          <t>-28,71%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -12,41</t>
+          <t>-23,46; -6,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -23,2</t>
+          <t>-33,86; -12,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -4,45</t>
+          <t>-32,92; -12,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -10,95</t>
+          <t>-49,05; -24,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -11,26</t>
+          <t>-25,12; -11,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -19,83</t>
+          <t>-36,97; -20,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Edad-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.08230427853742617</v>
+        <v>7.111306059392764</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.638978089824338</v>
+        <v>10.99468307216944</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-11.19197913915207</v>
+        <v>-9.015665150769447</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-28.39503949209393</v>
+        <v>-26.84428361045921</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-5.877714403474654</v>
+        <v>-1.547900268328434</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-16.91062266689209</v>
+        <v>-11.35390741223104</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-21.74425666568567</v>
+        <v>-12.69742634791291</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-28.47102314526617</v>
+        <v>-16.82762294925089</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-31.34024028511466</v>
+        <v>-27.19301239682805</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-50.19458136349024</v>
+        <v>-49.61642861092751</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-20.78123750502931</v>
+        <v>-15.38689886438497</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-35.85085126542609</v>
+        <v>-29.36246261180004</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>22.89757494158842</v>
+        <v>25.26195486335564</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>28.56471576769813</v>
+        <v>37.27611154053829</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11.60422786646699</v>
+        <v>9.313921118912578</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.9270882858894984</v>
+        <v>-1.742232852475573</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.828221628743256</v>
+        <v>11.99251020734716</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.536749793272375</v>
+        <v>7.445337130734202</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.001523413159659762</v>
+        <v>0.1628399273214345</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01182718138194976</v>
+        <v>0.251764356285793</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.1919388588413761</v>
+        <v>-0.158840118427598</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.4869658358996216</v>
+        <v>-0.4729489301657858</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.1043234179417338</v>
+        <v>-0.03047974165763762</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.3001462532936675</v>
+        <v>-0.2235700657273296</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.341677336644536</v>
+        <v>-0.2363293643751918</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.4825122551603766</v>
+        <v>-0.3522319691273544</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.4777764308582606</v>
+        <v>-0.4243700638696275</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.7961471316462062</v>
+        <v>-0.7986709429960976</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3300417948081873</v>
+        <v>-0.2725139767049111</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.6006010790927711</v>
+        <v>-0.535838487809477</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.5593425528558846</v>
+        <v>0.6913950797801517</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.6727148531327988</v>
+        <v>0.9992175611400637</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.2543720528278881</v>
+        <v>0.1833556310622524</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.005070797399745573</v>
+        <v>-0.01741649250292705</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1783427976035333</v>
+        <v>0.2667300178542469</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02162190511598107</v>
+        <v>0.1653840403581373</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-13.25099797455414</v>
+        <v>-11.81921261150814</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-13.12934986430863</v>
+        <v>-10.60517100784368</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-12.09780868598157</v>
+        <v>-12.06005326220256</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-10.73508403245984</v>
+        <v>-9.190434494946526</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-12.47052124807714</v>
+        <v>-11.70333952890469</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-11.50490009365535</v>
+        <v>-9.631579833224579</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-20.85060140779274</v>
+        <v>-19.17334698286416</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-23.05370511344869</v>
+        <v>-20.75451678876483</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-20.2795424733203</v>
+        <v>-19.61687565893671</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-22.97931782483974</v>
+        <v>-19.98773314470447</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-18.51927877276881</v>
+        <v>-16.80995586524996</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-19.5784802652872</v>
+        <v>-17.28669119084706</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-4.506491894418954</v>
+        <v>-4.212315591440047</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-1.163927153609005</v>
+        <v>0.05122939651240774</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-4.213725371545528</v>
+        <v>-4.423221106489257</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1.608774769948924</v>
+        <v>2.731907492990791</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-6.370900587035579</v>
+        <v>-6.45803942933613</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-3.709294616024142</v>
+        <v>-1.200601018865676</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.2107145572770088</v>
+        <v>-0.1980361834546808</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.2087801348476045</v>
+        <v>-0.1776943744317335</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.2366501107488227</v>
+        <v>-0.2368186174382285</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.2099933046654404</v>
+        <v>-0.1804690197821189</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2176215298937834</v>
+        <v>-0.2105970945976166</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.2007705940954524</v>
+        <v>-0.1733165755169652</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.3197996704570934</v>
+        <v>-0.3008950080211293</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.3545818703543487</v>
+        <v>-0.3348148131376276</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.3635612576305772</v>
+        <v>-0.363357428481863</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.4220172524154148</v>
+        <v>-0.3705153814966886</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.3105667515125633</v>
+        <v>-0.2894343260977409</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.3327019725250763</v>
+        <v>-0.3071289450156117</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.07680470371134814</v>
+        <v>-0.07288355404936753</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-0.02090891324132069</v>
+        <v>0.001348328674367325</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.08340036938657498</v>
+        <v>-0.09782854655889933</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.03021267899212158</v>
+        <v>0.05492858238822897</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1170769280281122</v>
+        <v>-0.1206727089502745</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.06712242092057152</v>
+        <v>-0.02358732554738825</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-2.486771630014073</v>
+        <v>-4.003429259649427</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-8.346680464662315</v>
+        <v>-9.48356156825092</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-16.16027270727854</v>
+        <v>-14.5828409821704</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-15.4500495453183</v>
+        <v>-11.70391606869268</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-9.333828735966055</v>
+        <v>-9.360549767896288</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-11.38569370353316</v>
+        <v>-10.22446649836851</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-11.76087197094395</v>
+        <v>-13.15958473937581</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-19.89480208414465</v>
+        <v>-20.34606092302524</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-25.88957378485402</v>
+        <v>-23.50007508363719</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-27.13478051326009</v>
+        <v>-24.05278773653967</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-15.63910294689226</v>
+        <v>-15.48978471145094</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-20.26715126084354</v>
+        <v>-18.36947922458046</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>7.060999306996544</v>
+        <v>4.493087387079602</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>5.016341071383375</v>
+        <v>2.185008240894268</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-6.406316978199393</v>
+        <v>-5.155245871640078</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-3.979000395495558</v>
+        <v>-1.030567205067741</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-2.091706954445911</v>
+        <v>-2.912862155390754</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-2.970203678752858</v>
+        <v>-2.051220278562397</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.04651061197168986</v>
+        <v>-0.0735786228159984</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.1561097173773838</v>
+        <v>-0.1742974221164924</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.3012452923540835</v>
+        <v>-0.285934443245618</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.2880059499285691</v>
+        <v>-0.2294856488517374</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.1742843899513463</v>
+        <v>-0.1775727076733292</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2125975028497007</v>
+        <v>-0.1939614921825878</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.2014224140302542</v>
+        <v>-0.220951870723958</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.3424562595338012</v>
+        <v>-0.3553688647558418</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.4431745816297078</v>
+        <v>-0.4253554397233619</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.4663992862812168</v>
+        <v>-0.4446028425513296</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.2734109344934304</v>
+        <v>-0.2776729088385572</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.3591472091057814</v>
+        <v>-0.3362152506977188</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.1466542024023849</v>
+        <v>0.09342990791575807</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.09866981831810519</v>
+        <v>0.04413882953938315</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.129794210148759</v>
+        <v>-0.1157176678126093</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.07691418743361422</v>
+        <v>-0.02610022778674353</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.04142660164439006</v>
+        <v>-0.05938615906275265</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.05785789182539746</v>
+        <v>-0.04236095997557957</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-9.280578568980053</v>
+        <v>-6.19553869103423</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-9.051035150203646</v>
+        <v>-7.2509970008311</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-2.58458923664758</v>
+        <v>-5.295131156252339</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-12.26383039959289</v>
+        <v>-13.7639150842616</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-5.979406392799125</v>
+        <v>-5.707435999971561</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-9.962463376985845</v>
+        <v>-9.656469389705819</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-18.11469914324862</v>
+        <v>-15.18706833670853</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-20.75232899611182</v>
+        <v>-16.97416496503958</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-11.3733742629701</v>
+        <v>-14.31151752388099</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-21.11680880065942</v>
+        <v>-21.93324572686784</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-12.27565876922159</v>
+        <v>-11.29023502328928</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-16.48570617103832</v>
+        <v>-16.26582905420551</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-0.5519934835648244</v>
+        <v>2.413269077605008</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1.272991509699167</v>
+        <v>3.305520985097996</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4.851670247376487</v>
+        <v>2.190461948310024</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-3.254950219670982</v>
+        <v>-5.299379550286451</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.2796957563453474</v>
+        <v>0.09665582431270305</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-2.168473534670714</v>
+        <v>-2.383107318435476</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.2242130816721451</v>
+        <v>-0.1546357333341919</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.2186674535716037</v>
+        <v>-0.1809791358821083</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.09561126182867327</v>
+        <v>-0.1879400508212288</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.4536737531565455</v>
+        <v>-0.4885225359112769</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1741794021667934</v>
+        <v>-0.1668572332006228</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.2902053817920289</v>
+        <v>-0.282307460803914</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.4000729746820411</v>
+        <v>-0.344129409044091</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.4446925996377745</v>
+        <v>-0.4032103852740505</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.3652005193518428</v>
+        <v>-0.4504192752012265</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.6707322287048756</v>
+        <v>-0.6993060529986853</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.3264502293267673</v>
+        <v>-0.31903892647079</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.4554040485324439</v>
+        <v>-0.441580821188998</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-0.0145352225297619</v>
+        <v>0.07316870536763814</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.03544215117925307</v>
+        <v>0.08901316601891719</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.2158163754470075</v>
+        <v>0.09700033972362575</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.1190696902655735</v>
+        <v>-0.2167305018808225</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.008165130084735815</v>
+        <v>0.002855305433528147</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.07126887437731154</v>
+        <v>-0.05872860915400215</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-8.32579242345629</v>
+        <v>-6.958859408935991</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-12.60069356068003</v>
+        <v>-10.87125575883014</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-10.25460147098062</v>
+        <v>-10.70933135887874</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-17.06825775079078</v>
+        <v>-16.06145267180248</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-9.191923394149647</v>
+        <v>-8.677639236170853</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-14.2007569465679</v>
+        <v>-12.87706306270158</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-13.25042111320459</v>
+        <v>-11.63589059199919</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-18.76659200769538</v>
+        <v>-17.00494092666229</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-15.40815857156266</v>
+        <v>-15.40827692272912</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-22.84995588658888</v>
+        <v>-21.49067144938049</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-12.73581157673944</v>
+        <v>-11.96284746678382</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-18.69903729521868</v>
+        <v>-17.17436358614127</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-3.081794520635174</v>
+        <v>-2.131597794921965</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-6.635647397371643</v>
+        <v>-4.210654515134935</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-5.419832303612407</v>
+        <v>-5.954766706598869</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-10.41090064567243</v>
+        <v>-9.142804562176991</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-5.541073835820444</v>
+        <v>-5.416984652203325</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-9.744870110091576</v>
+        <v>-8.602605151423765</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.1550759644441405</v>
+        <v>-0.1339769113739462</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2347001471094009</v>
+        <v>-0.209301148900059</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.2276652148271062</v>
+        <v>-0.2389945580816009</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.3789370633812267</v>
+        <v>-0.3584350558229324</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.1858428352979701</v>
+        <v>-0.1790609693768958</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.2871117198395308</v>
+        <v>-0.2657150559017968</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.2346496920150425</v>
+        <v>-0.2149353384214662</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.3386070483581766</v>
+        <v>-0.3184251897886948</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.329164891411815</v>
+        <v>-0.3268659071585072</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.4905184027618657</v>
+        <v>-0.4700625846438216</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.2511580052419535</v>
+        <v>-0.2385459607558895</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.3696889872857413</v>
+        <v>-0.3476580540860886</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.06074887369775376</v>
+        <v>-0.04763772599944401</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.1281302121978793</v>
+        <v>-0.08789696238405113</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.1280573769471604</v>
+        <v>-0.1412282835570448</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.2441911100374952</v>
+        <v>-0.212911852004096</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1172772872610775</v>
+        <v>-0.1139575865841379</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.2013796972570646</v>
+        <v>-0.1850933172479575</v>
       </c>
     </row>
     <row r="34">
